--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_270_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_270_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9261</v>
+        <v>6.4884</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9741</v>
+        <v>5.1668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9519</v>
+        <v>1.3216</v>
       </c>
       <c r="G2" t="n">
         <v>5.6796</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6814</v>
+        <v>-0.119</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3734</v>
+        <v>-0.1808</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3079</v>
+        <v>0.0617</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4377</v>
+        <v>6.3044</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1415</v>
+        <v>5.5596</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2962</v>
+        <v>0.7448</v>
       </c>
       <c r="G3" t="n">
-        <v>3.552</v>
+        <v>2.987</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7729</v>
+        <v>-1.0346</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2208</v>
+        <v>4.0217</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6531</v>
+        <v>3.6877</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2383</v>
+        <v>-0.6015</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4148</v>
+        <v>4.2892</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1011</v>
+        <v>-0.7007</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4655</v>
+        <v>-0.4331</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.2676</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1598</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8314</v>
+        <v>0.5493</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>0.4955</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0056</v>
+        <v>0.0538</v>
       </c>
       <c r="V3" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6327</v>
+        <v>5.1069</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3919</v>
+        <v>4.2476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2407</v>
+        <v>0.8593</v>
       </c>
       <c r="G4" t="n">
-        <v>2.987</v>
+        <v>3.552</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0346</v>
+        <v>3.7729</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0217</v>
+        <v>-0.2208</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6877</v>
+        <v>4.6531</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6015</v>
+        <v>4.2383</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2892</v>
+        <v>0.4148</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7007</v>
+        <v>-1.1011</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4331</v>
+        <v>-0.4655</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2676</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1224</v>
+        <v>1.5007</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6721</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4503</v>
+        <v>0.5687</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2935</v>
+        <v>4.2942</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3819</v>
+        <v>3.6178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9116</v>
+        <v>0.6763</v>
       </c>
       <c r="G5" t="n">
         <v>3.8895</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4362</v>
+        <v>-0.4356</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1375</v>
+        <v>-0.3727</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0746</v>
+        <v>3.5911</v>
       </c>
       <c r="E6" t="n">
-        <v>2.241</v>
+        <v>2.7793</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8336</v>
+        <v>0.8117</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9792</v>
+        <v>2.523</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1332</v>
+        <v>0.6627</v>
       </c>
       <c r="I6" t="n">
-        <v>0.154</v>
+        <v>1.8603</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3398</v>
+        <v>3.1055</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3963</v>
+        <v>0.8739</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7361</v>
+        <v>2.2317</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.319</v>
+        <v>-0.5825</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7369</v>
+        <v>-0.2112</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2341</v>
+        <v>-0.1819</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4732</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7609</v>
+        <v>-0.0876</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8197</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0617</v>
+        <v>2.9939</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3508</v>
+        <v>2.002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7109</v>
+        <v>0.9919</v>
       </c>
       <c r="G7" t="n">
-        <v>2.523</v>
+        <v>2.5052</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6627</v>
+        <v>2.2341</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8603</v>
+        <v>0.2711</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1055</v>
+        <v>3.0594</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8739</v>
+        <v>2.5207</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2317</v>
+        <v>0.5386</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5825</v>
+        <v>-0.5542</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2112</v>
+        <v>-0.2866</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.2676</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7112000000000001</v>
+        <v>1.0042</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>0.3343</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1885</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1326</v>
+        <v>2.249</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2168</v>
+        <v>1.6021</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="G8" t="n">
         <v>1.0265</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6423</v>
+        <v>0.7587</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>0.0119</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0157</v>
+        <v>0.7468</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1294</v>
+        <v>2.028</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0702</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0591</v>
+        <v>2.019</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5052</v>
+        <v>-0.2098</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2341</v>
+        <v>0.6433</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2711</v>
+        <v>-0.8532</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0594</v>
+        <v>0.5407</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5207</v>
+        <v>1.1798</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5386</v>
+        <v>-0.6391</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5542</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2866</v>
+        <v>-0.5365</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2676</v>
+        <v>-0.214</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1397</v>
+        <v>0.2869</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.2122</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7372</v>
+        <v>0.4991</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2836</v>
+        <v>1.719</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7772</v>
+        <v>1.698</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3762</v>
+        <v>0.9316</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1534</v>
+        <v>0.7664</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2098</v>
+        <v>-0.9792</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6433</v>
+        <v>-1.1332</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8532</v>
+        <v>0.154</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5407</v>
+        <v>0.3398</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1798</v>
+        <v>-0.3963</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6391</v>
+        <v>0.7361</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-1.319</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5365</v>
+        <v>-0.7369</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.214</v>
+        <v>-0.5821</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.036</v>
+        <v>1.8576</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>1.1639</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6335</v>
+        <v>0.6937</v>
       </c>
       <c r="V10" t="n">
-        <v>1.719</v>
+        <v>0.8197</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1374</v>
+        <v>0.9322</v>
       </c>
       <c r="E11" t="n">
-        <v>0.278</v>
+        <v>-0.1624</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8593</v>
+        <v>1.0946</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4067</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.959</v>
+        <v>0.7538</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8259</v>
+        <v>0.3855</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1331</v>
+        <v>0.3684</v>
       </c>
       <c r="V11" t="n">
         <v>0.9615</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. NETZIPOGLOU</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0988</v>
+        <v>-0.6514</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2147</v>
+        <v>-1.0439</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8841</v>
+        <v>0.3925</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7397</v>
+        <v>-0.5471</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1609</v>
+        <v>0.7312</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5788</v>
+        <v>-1.2783</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4887</v>
+        <v>0.8901</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4887</v>
+        <v>1.5327</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.251</v>
+        <v>-1.4372</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6722</v>
+        <v>-0.8016</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5788</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3188</v>
+        <v>1.0554</v>
       </c>
       <c r="T12" t="n">
-        <v>1.274</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0448</v>
+        <v>0.438</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>O. NETZIPOGLOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2368</v>
+        <v>-1.9005</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6965</v>
+        <v>-1.0836</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4597</v>
+        <v>-0.8169</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5471</v>
+        <v>-2.7397</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7312</v>
+        <v>-2.1609</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2783</v>
+        <v>-0.5788</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8901</v>
+        <v>-1.4887</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5327</v>
+        <v>-1.4887</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6425999999999999</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4372</v>
+        <v>-1.251</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8016</v>
+        <v>-0.6722</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5788</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4701</v>
+        <v>0.5171</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0351</v>
+        <v>0.405</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5052</v>
+        <v>0.112</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.2673</v>
+        <v>33.1342</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7588</v>
+        <v>23.6259</v>
       </c>
       <c r="F14" t="n">
-        <v>9.508099999999999</v>
+        <v>9.5082</v>
       </c>
       <c r="G14" t="n">
         <v>15.2803</v>
       </c>
       <c r="H14" t="n">
-        <v>7.400500000000002</v>
+        <v>7.400499999999999</v>
       </c>
       <c r="I14" t="n">
         <v>7.879799999999999</v>
@@ -1528,10 +1528,10 @@
         <v>12.1282</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.258199999999999</v>
+        <v>-9.2582</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.009799999999999</v>
+        <v>-5.0098</v>
       </c>
       <c r="O14" t="n">
         <v>-4.2483</v>
@@ -1546,19 +1546,19 @@
         <v>15.077</v>
       </c>
       <c r="S14" t="n">
-        <v>5.680200000000001</v>
+        <v>7.5472</v>
       </c>
       <c r="T14" t="n">
-        <v>1.928499999999999</v>
+        <v>3.7955</v>
       </c>
       <c r="U14" t="n">
-        <v>3.751799999999999</v>
+        <v>3.7518</v>
       </c>
       <c r="V14" t="n">
         <v>6.827500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8897</v>
+        <v>6.889699999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-0.06220000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8261</v>
+        <v>1.7252</v>
       </c>
       <c r="E15" t="n">
         <v>1.0142</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8118</v>
+        <v>0.711</v>
       </c>
       <c r="G15" t="n">
         <v>1.3524</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.083</v>
+        <v>-0.1838</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0663</v>
+        <v>-0.0345</v>
       </c>
       <c r="V15" t="n">
         <v>0.7886</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.3916</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2452</v>
+        <v>2.0093</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7185</v>
+        <v>-1.6177</v>
       </c>
       <c r="G16" t="n">
         <v>0.668</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2315</v>
+        <v>-0.3666</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3536</v>
+        <v>-0.2528</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2959</v>
+        <v>-1.8038</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1208</v>
+        <v>-1.4557</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1751</v>
+        <v>-0.3481</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.391</v>
+        <v>-2.5458</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2857</v>
+        <v>0.8907</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6767</v>
+        <v>-3.4364</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5039</v>
+        <v>-0.7446</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1798</v>
+        <v>1.1126</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.8572</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8949</v>
+        <v>-1.8012</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8942</v>
+        <v>-0.222</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0008</v>
+        <v>-1.5792</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3993</v>
+        <v>-0.7194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5351</v>
+        <v>-0.8529</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1357</v>
+        <v>0.1336</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6934</v>
+        <v>-1.8279</v>
       </c>
       <c r="E19" t="n">
         <v>-0.007900000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6855</v>
+        <v>-1.8199</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2918</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3295</v>
+        <v>-0.4639</v>
       </c>
       <c r="T19" t="n">
         <v>0.0395</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.369</v>
+        <v>-0.5034</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0562</v>
+        <v>-1.8355</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5737</v>
+        <v>-0.8285</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4825</v>
+        <v>-1.007</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5458</v>
+        <v>-2.391</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8907</v>
+        <v>0.2857</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.4364</v>
+        <v>-2.6767</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7446</v>
+        <v>0.5039</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1126</v>
+        <v>1.1798</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8572</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8012</v>
+        <v>-2.8949</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.222</v>
+        <v>-0.8942</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5792</v>
+        <v>-2.0008</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9717</v>
+        <v>-0.1404</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.1727</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0009</v>
+        <v>0.0323</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6687</v>
+        <v>-2.9382</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9769</v>
+        <v>0.741</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6457</v>
+        <v>-3.6793</v>
       </c>
       <c r="G21" t="n">
         <v>1.2118</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.329</v>
+        <v>-0.5985</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1766</v>
+        <v>-0.4125</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1524</v>
+        <v>-0.186</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7064</v>
+        <v>-4.1502</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8123</v>
+        <v>-0.2225</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8941</v>
+        <v>-3.9277</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6401</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.422</v>
+        <v>-0.8659</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.4479</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3844</v>
+        <v>-0.418</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7886</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1659</v>
+        <v>-5.8964</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1161</v>
+        <v>-3.8802</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0498</v>
+        <v>-2.0162</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5599</v>
@@ -2248,13 +2248,13 @@
         <v>2.3195</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5854</v>
+        <v>-1.3159</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1554</v>
+        <v>-0.9195</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4301</v>
+        <v>-0.3965</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7886</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.336</v>
+        <v>-6.6283</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6639</v>
+        <v>-2.9562</v>
       </c>
       <c r="F24" t="n">
         <v>-3.6721</v>
@@ -2326,10 +2326,10 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4506</v>
+        <v>-0.7429</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4189</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U24" t="n">
         <v>-0.0316</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4655</v>
+        <v>-8.0717</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0763</v>
+        <v>-3.5481</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.3893</v>
+        <v>-4.5237</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5232</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3233</v>
+        <v>-0.2829</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4604</v>
+        <v>-0.0114</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1371</v>
+        <v>-0.2715</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5697</v>
@@ -2440,10 +2440,10 @@
         <v>-31.2672</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.3667</v>
+        <v>-9.366599999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.9008</v>
+        <v>-21.9007</v>
       </c>
       <c r="G26" t="n">
         <v>-15.2803</v>
@@ -2482,16 +2482,16 @@
         <v>11.5976</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.680099999999999</v>
+        <v>-5.680199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7517</v>
+        <v>-3.7518</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.9285</v>
+        <v>-1.9284</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.827400000000001</v>
+        <v>-6.8274</v>
       </c>
       <c r="W26" t="n">
         <v>0.204</v>
